--- a/pensum/ok05/LOM_Ovingsark_Okonomistyring_kap05_Timepris_og_kalkyle_NY.xlsx
+++ b/pensum/ok05/LOM_Ovingsark_Okonomistyring_kap05_Timepris_og_kalkyle_NY.xlsx
@@ -610,6 +610,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -677,6 +678,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -694,10 +696,11 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Merk: timeprisen skal dekke alt bedriften ikke får igjen gjennom materiell og underentreprenører.</t>
-        </is>
-      </c>
-    </row>
+          <t>Merk: timeprisen skal dekke alt bedriften ikke får igjen gjennom materiellet som faktureres videre med påslag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -712,6 +715,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -736,6 +740,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -896,6 +901,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
@@ -924,6 +930,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
@@ -948,7 +955,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+          <t>Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
         </is>
       </c>
     </row>
@@ -988,6 +995,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1040,6 +1048,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
@@ -1083,6 +1092,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
@@ -1097,7 +1107,7 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>5180000</v>
+        <v>8440000</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
@@ -1133,11 +1143,11 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Varekostnad underentreprenør</t>
+          <t>Varekostnad innleide montører</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>3660000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="18">
@@ -1191,6 +1201,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -1201,7 +1212,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>− materiell og underentreprenør fakturert videre</t>
+          <t>− materiell fakturert videre</t>
         </is>
       </c>
       <c r="B24" s="14" t="n">
@@ -1250,6 +1261,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
@@ -1330,6 +1342,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
@@ -1379,6 +1392,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
@@ -1419,6 +1433,7 @@
         <v/>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
@@ -1458,6 +1473,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
@@ -1468,7 +1484,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 5.2 og formelsamlingen (timelønn, faktureringsgrad). Tallene er Nordlys Elektro AS sitt regnskap for 2026.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 5.2 og formelsamlingen (timelønn, faktureringsgrad). Tallene er Nordlys Elektro AS sitt regnskap for 2026.</t>
         </is>
       </c>
     </row>
@@ -1523,6 +1539,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1703,6 +1720,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -1769,6 +1787,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -1825,6 +1844,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
@@ -1865,6 +1885,7 @@
         <v/>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
@@ -1931,6 +1952,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2129,6 +2151,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
@@ -2215,6 +2238,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -2304,6 +2328,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
@@ -2496,6 +2521,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
@@ -2528,6 +2554,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
@@ -2568,6 +2595,7 @@
         <v/>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
@@ -2578,7 +2606,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 5.2, 5.2.1 og avsnittet om for- og etterkalkyle. Oppdraget er Nordlys' eget.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 5.2, 5.2.1 og avsnittet om for- og etterkalkyle. Oppdraget er Nordlys' eget.</t>
         </is>
       </c>
     </row>
@@ -2635,6 +2663,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2697,6 +2726,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
@@ -2991,6 +3021,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -3019,6 +3050,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
@@ -3048,10 +3080,11 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 5.2 og formelsamlingen. Tallene er Nordlys Elektro AS sine egne.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 5.2 og formelsamlingen. Tallene er Nordlys Elektro AS sine egne.</t>
         </is>
       </c>
     </row>
@@ -3102,6 +3135,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3116,6 +3150,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="9" t="inlineStr"/>
       <c r="B7" s="9" t="inlineStr">
@@ -3314,6 +3349,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
@@ -3332,6 +3368,8 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
@@ -3346,6 +3384,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
@@ -3448,6 +3487,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -3533,6 +3573,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
@@ -3547,6 +3588,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
@@ -3638,6 +3680,7 @@
         <v/>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
@@ -3715,6 +3758,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
@@ -3744,10 +3788,11 @@
         <v/>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 5.2, kap. 2 om faste og variable kostnader og kap. 7 om hvilke oppdrag som prioriteres. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+          <t>Kilde: Økonomistyring for LØM-emnet, kap. 5.2, kap. 2 om faste og variable kostnader og kap. 7 om hvilke oppdrag som prioriteres. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
         </is>
       </c>
     </row>

--- a/pensum/ok05/LOM_Ovingsark_Okonomistyring_kap05_Timepris_og_kalkyle_NY.xlsx
+++ b/pensum/ok05/LOM_Ovingsark_Okonomistyring_kap05_Timepris_og_kalkyle_NY.xlsx
@@ -604,7 +604,7 @@
     <t xml:space="preserve">Prøv dette: sett B8 til lærebokas påslag for indirekte kostnader og B11 til fortjenesteprosenten, og les av B22, B23 og B29. Det er oppgave 2.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 avsnitt 5.1 og 5.1.2. Materiellpåslaget er Nordlys Elektro AS' eget.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet, avsnitt 5.1 og 5.1.2. Materiellpåslaget er Nordlys Elektro AS' eget.</t>
   </si>
   <si>
     <t xml:space="preserve">Ett oppdrag: fra kostnad til kundens pris</t>
